--- a/Outputs/Scenarios/PtX_demand_CY_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_CY_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0007576705983832278</v>
+        <v>0.0008210627489166696</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001262784330638713</v>
+        <v>0.001193154138652529</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0005051137322554853</v>
+        <v>0.000511351773708227</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.004089523146886638</v>
+        <v>0.00443168195242908</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.00681587191147773</v>
+        <v>0.006440043309368465</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.002726348764591092</v>
+        <v>0.002760018561157914</v>
       </c>
     </row>
     <row r="43">
